--- a/storage/Librarie_Saint_Laurent.xlsx
+++ b/storage/Librarie_Saint_Laurent.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="350">
   <si>
     <t>Book_name</t>
   </si>
@@ -27,1008 +27,861 @@
     <t>Author_name</t>
   </si>
   <si>
+    <t>Reviews</t>
+  </si>
+  <si>
     <t>Publication_Year</t>
   </si>
   <si>
-    <t>Reviews</t>
-  </si>
-  <si>
     <t>Opportunity crime degree.</t>
   </si>
   <si>
     <t>James Vazquez</t>
   </si>
   <si>
+    <t>No reviews yet</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>Wide cultural season follow culture.</t>
+  </si>
+  <si>
+    <t>1998</t>
+  </si>
+  <si>
+    <t>Color generation.</t>
+  </si>
+  <si>
+    <t>Matthew May</t>
+  </si>
+  <si>
+    <t>1976</t>
+  </si>
+  <si>
+    <t>Day later serve.</t>
+  </si>
+  <si>
+    <t>Stephanie Cherry</t>
+  </si>
+  <si>
+    <t>1992</t>
+  </si>
+  <si>
+    <t>Will since.</t>
+  </si>
+  <si>
+    <t>Timothy Newman</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>Think but manage kitchen.</t>
+  </si>
+  <si>
+    <t>Amy Potter</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>Service another pressure long edge.</t>
+  </si>
+  <si>
+    <t>Jody Clark</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>Investment but second.</t>
+  </si>
+  <si>
+    <t>Yvonne Rodriguez</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>Again relationship another.</t>
+  </si>
+  <si>
+    <t>Heidi Hicks</t>
+  </si>
+  <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>Son get usually size.</t>
+  </si>
+  <si>
+    <t>Lauren Clark</t>
+  </si>
+  <si>
+    <t>1987</t>
+  </si>
+  <si>
+    <t>Develop manage she quality.</t>
+  </si>
+  <si>
+    <t>Mathew Henderson</t>
+  </si>
+  <si>
+    <t>1972</t>
+  </si>
+  <si>
+    <t>Expect civil sometimes.</t>
+  </si>
+  <si>
+    <t>Melissa Clark</t>
+  </si>
+  <si>
+    <t>1974</t>
+  </si>
+  <si>
+    <t>Describe friend light certain.</t>
+  </si>
+  <si>
+    <t>Robert Marshall</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>Gas force leader word pattern.</t>
+  </si>
+  <si>
+    <t>James Nguyen</t>
+  </si>
+  <si>
+    <t>1988</t>
+  </si>
+  <si>
+    <t>Fire about line draw.</t>
+  </si>
+  <si>
+    <t>Pamela Brown</t>
+  </si>
+  <si>
+    <t>Pull parent service network.</t>
+  </si>
+  <si>
+    <t>Dominique Arellano</t>
+  </si>
+  <si>
+    <t>Particularly market order.</t>
+  </si>
+  <si>
+    <t>Stephanie Yoder</t>
+  </si>
+  <si>
+    <t>Small to agreement president edge.</t>
+  </si>
+  <si>
+    <t>Matthew Boyer</t>
+  </si>
+  <si>
+    <t>Analysis letter so well could.</t>
+  </si>
+  <si>
+    <t>Christine Martin</t>
+  </si>
+  <si>
+    <t>1981</t>
+  </si>
+  <si>
+    <t>Head us song glass.</t>
+  </si>
+  <si>
+    <t>Eric Knight</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>Dream three.</t>
+  </si>
+  <si>
+    <t>Laura Hartman</t>
+  </si>
+  <si>
+    <t>Hot language however blood player.</t>
+  </si>
+  <si>
+    <t>Stephanie Miller</t>
+  </si>
+  <si>
+    <t>1993</t>
+  </si>
+  <si>
+    <t>Audience there.</t>
+  </si>
+  <si>
+    <t>Amanda Williams</t>
+  </si>
+  <si>
+    <t>Move case.</t>
+  </si>
+  <si>
+    <t>Tammy Jordan</t>
+  </si>
+  <si>
+    <t>A full fine model more.</t>
+  </si>
+  <si>
+    <t>Sophia Horton</t>
+  </si>
+  <si>
+    <t>Control much run institution.</t>
+  </si>
+  <si>
+    <t>Sandra Douglas</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Speech simply sort.</t>
+  </si>
+  <si>
+    <t>Paul Burnett</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>Whether politics training experience.</t>
+  </si>
+  <si>
+    <t>Jill Harvey</t>
+  </si>
+  <si>
+    <t>Cause power four.</t>
+  </si>
+  <si>
+    <t>Brittany Perez</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>Material finally into better.</t>
+  </si>
+  <si>
+    <t>Jessica Oliver</t>
+  </si>
+  <si>
+    <t>Air true out reflect.</t>
+  </si>
+  <si>
+    <t>Stacey Johnson</t>
+  </si>
+  <si>
+    <t>Although guess race page result.</t>
+  </si>
+  <si>
+    <t>Thomas Wright</t>
+  </si>
+  <si>
+    <t>1977</t>
+  </si>
+  <si>
+    <t>Nature back smile.</t>
+  </si>
+  <si>
+    <t>Allen Harris</t>
+  </si>
+  <si>
+    <t>1978</t>
+  </si>
+  <si>
+    <t>Collection how bag big.</t>
+  </si>
+  <si>
+    <t>Dale Blackburn</t>
+  </si>
+  <si>
+    <t>1985</t>
+  </si>
+  <si>
+    <t>Nor issue edge pattern.</t>
+  </si>
+  <si>
+    <t>Amy Fitzpatrick</t>
+  </si>
+  <si>
+    <t>1979</t>
+  </si>
+  <si>
+    <t>Wrong smile live interesting.</t>
+  </si>
+  <si>
+    <t>Gregory Mccormick</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>Too have pass through.</t>
+  </si>
+  <si>
+    <t>Melissa Kelley</t>
+  </si>
+  <si>
+    <t>Allow opportunity dinner.</t>
+  </si>
+  <si>
+    <t>Ruben Stewart</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>Fine cause daughter half region.</t>
+  </si>
+  <si>
+    <t>Ryan Flynn</t>
+  </si>
+  <si>
+    <t>Want throw should.</t>
+  </si>
+  <si>
+    <t>Career late term.</t>
+  </si>
+  <si>
+    <t>Stefanie Manning</t>
+  </si>
+  <si>
+    <t>1970</t>
+  </si>
+  <si>
+    <t>Minute training cover.</t>
+  </si>
+  <si>
+    <t>Johnny Brewer</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>Expect economic natural.</t>
+  </si>
+  <si>
+    <t>James Fletcher</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>Science my population.</t>
+  </si>
+  <si>
+    <t>Julie Williams</t>
+  </si>
+  <si>
+    <t>Office kind mission change interesting.</t>
+  </si>
+  <si>
+    <t>Shannon Harrell DVM</t>
+  </si>
+  <si>
+    <t>Simply health item former.</t>
+  </si>
+  <si>
+    <t>Brad Lin</t>
+  </si>
+  <si>
+    <t>Reveal whose leave.</t>
+  </si>
+  <si>
+    <t>Lauren Gregory</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>This include price.</t>
+  </si>
+  <si>
+    <t>Andrew Brown</t>
+  </si>
+  <si>
+    <t>1986</t>
+  </si>
+  <si>
+    <t>May nation large support ago.</t>
+  </si>
+  <si>
+    <t>Mark Perkins</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>Feel himself court every.</t>
+  </si>
+  <si>
+    <t>Tracy Murphy</t>
+  </si>
+  <si>
+    <t>1975</t>
+  </si>
+  <si>
+    <t>Thing television generation let.</t>
+  </si>
+  <si>
+    <t>Kristen Cameron</t>
+  </si>
+  <si>
+    <t>Actually process improve back.</t>
+  </si>
+  <si>
+    <t>Sarah Shea</t>
+  </si>
+  <si>
+    <t>1997</t>
+  </si>
+  <si>
+    <t>Many must cultural have.</t>
+  </si>
+  <si>
+    <t>James Frazier</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>Use public.</t>
+  </si>
+  <si>
+    <t>Joanna Moreno</t>
+  </si>
+  <si>
+    <t>Soon though.</t>
+  </si>
+  <si>
+    <t>Todd Werner</t>
+  </si>
+  <si>
+    <t>Reveal executive worker police.</t>
+  </si>
+  <si>
+    <t>Jacqueline Huffman</t>
+  </si>
+  <si>
+    <t>Car particularly.</t>
+  </si>
+  <si>
+    <t>Kyle Leach</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>Country sing.</t>
+  </si>
+  <si>
+    <t>William Ray</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>Week support.</t>
+  </si>
+  <si>
+    <t>Robin Green</t>
+  </si>
+  <si>
+    <t>Although black.</t>
+  </si>
+  <si>
+    <t>Patricia Gardner</t>
+  </si>
+  <si>
+    <t>1991</t>
+  </si>
+  <si>
+    <t>Computer rule big star.</t>
+  </si>
+  <si>
+    <t>Kelly Galloway</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Group billion.</t>
+  </si>
+  <si>
+    <t>Jennifer Wright</t>
+  </si>
+  <si>
+    <t>Professor better development.</t>
+  </si>
+  <si>
+    <t>Ryan Woodward</t>
+  </si>
+  <si>
+    <t>1980</t>
+  </si>
+  <si>
+    <t>Include surface per.</t>
+  </si>
+  <si>
+    <t>Jonathan Harvey</t>
+  </si>
+  <si>
+    <t>Heart development.</t>
+  </si>
+  <si>
+    <t>Sarah Ford</t>
+  </si>
+  <si>
     <t>2023</t>
   </si>
   <si>
-    <t>No reviews yet</t>
-  </si>
-  <si>
-    <t>Wide cultural season follow culture.</t>
-  </si>
-  <si>
-    <t>Amy Dawson</t>
+    <t>Thousand serious experience take dark.</t>
+  </si>
+  <si>
+    <t>Christopher Howard</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Statement according car.</t>
+  </si>
+  <si>
+    <t>Nicole Berry</t>
+  </si>
+  <si>
+    <t>Change modern.</t>
+  </si>
+  <si>
+    <t>Michael Boyer</t>
+  </si>
+  <si>
+    <t>Set entire institution drop.</t>
+  </si>
+  <si>
+    <t>Sabrina Bishop</t>
+  </si>
+  <si>
+    <t>Leave not.</t>
+  </si>
+  <si>
+    <t>Michael Thompson</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>Green road.</t>
+  </si>
+  <si>
+    <t>Chris Wilkerson</t>
+  </si>
+  <si>
+    <t>Service man admit.</t>
+  </si>
+  <si>
+    <t>Joel Barber</t>
+  </si>
+  <si>
+    <t>1973</t>
+  </si>
+  <si>
+    <t>Research finally fish paper.</t>
+  </si>
+  <si>
+    <t>April Alvarado</t>
+  </si>
+  <si>
+    <t>At food hold.</t>
+  </si>
+  <si>
+    <t>David Logan</t>
+  </si>
+  <si>
+    <t>Nothing reveal set evidence there.</t>
+  </si>
+  <si>
+    <t>Andrea Page</t>
+  </si>
+  <si>
+    <t>Sea somebody character join.</t>
+  </si>
+  <si>
+    <t>Miss Morgan Griffin</t>
+  </si>
+  <si>
+    <t>Hard sell mean.</t>
+  </si>
+  <si>
+    <t>Cole Cook</t>
+  </si>
+  <si>
+    <t>Agreement pull rock very development.</t>
+  </si>
+  <si>
+    <t>Matthew Jones</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>Evidence just author same.</t>
+  </si>
+  <si>
+    <t>Brian Silva</t>
+  </si>
+  <si>
+    <t>Talk once recognize.</t>
+  </si>
+  <si>
+    <t>Paula Maddox</t>
+  </si>
+  <si>
+    <t>But process cut suddenly factor.</t>
+  </si>
+  <si>
+    <t>John Hickman</t>
+  </si>
+  <si>
+    <t>Peace determine we.</t>
+  </si>
+  <si>
+    <t>Charlotte Costa</t>
+  </si>
+  <si>
+    <t>Effect local purpose every.</t>
+  </si>
+  <si>
+    <t>Tamara Richardson</t>
+  </si>
+  <si>
+    <t>There store.</t>
+  </si>
+  <si>
+    <t>Robin Young</t>
+  </si>
+  <si>
+    <t>Huge require.</t>
+  </si>
+  <si>
+    <t>Joshua Gibson</t>
+  </si>
+  <si>
+    <t>Expert report information even.</t>
+  </si>
+  <si>
+    <t>Say not too.</t>
+  </si>
+  <si>
+    <t>Maria Williams</t>
+  </si>
+  <si>
+    <t>Near guy condition.</t>
+  </si>
+  <si>
+    <t>Shannon Johnson</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>Yourself not place fine.</t>
+  </si>
+  <si>
+    <t>Charles Werner</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>Owner audience spring president space.</t>
+  </si>
+  <si>
+    <t>Annette Leon</t>
+  </si>
+  <si>
+    <t>Quality structure seven.</t>
+  </si>
+  <si>
+    <t>Jordan Jenkins</t>
+  </si>
+  <si>
+    <t>Skill majority another.</t>
+  </si>
+  <si>
+    <t>Christopher Gordon</t>
+  </si>
+  <si>
+    <t>Choose subject.</t>
+  </si>
+  <si>
+    <t>Danielle Le</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>Question work night.</t>
+  </si>
+  <si>
+    <t>Sarah Carpenter</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>Plant director increase decide one.</t>
+  </si>
+  <si>
+    <t>John Bishop</t>
+  </si>
+  <si>
+    <t>Democratic produce together material.</t>
+  </si>
+  <si>
+    <t>Rachel Davis</t>
+  </si>
+  <si>
+    <t>Six who middle.</t>
+  </si>
+  <si>
+    <t>Joshua Reeves</t>
+  </si>
+  <si>
+    <t>Hair tax.</t>
+  </si>
+  <si>
+    <t>Traci Scott</t>
+  </si>
+  <si>
+    <t>Less respond write lose.</t>
+  </si>
+  <si>
+    <t>Jesse Delgado</t>
+  </si>
+  <si>
+    <t>Time if election.</t>
+  </si>
+  <si>
+    <t>Alicia Bennett</t>
+  </si>
+  <si>
+    <t>Seek wish project.</t>
+  </si>
+  <si>
+    <t>Elizabeth Ryan</t>
+  </si>
+  <si>
+    <t>Stand between.</t>
+  </si>
+  <si>
+    <t>Chad Hall</t>
+  </si>
+  <si>
+    <t>Protect democratic.</t>
+  </si>
+  <si>
+    <t>Ray Bryant DDS</t>
   </si>
   <si>
     <t>1983</t>
   </si>
   <si>
-    <t>Least tend establish.</t>
-  </si>
-  <si>
-    <t>Devin Martinez</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>To bag responsibility final.</t>
-  </si>
-  <si>
-    <t>Brian Matthews</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>Support industry air forget national.</t>
-  </si>
-  <si>
-    <t>Emma King</t>
-  </si>
-  <si>
-    <t>1985</t>
-  </si>
-  <si>
-    <t>Project address series.</t>
-  </si>
-  <si>
-    <t>Casey Conner</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>Talk leg dinner.</t>
-  </si>
-  <si>
-    <t>Raissa IRUTINGABO</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>Enter back.</t>
-  </si>
-  <si>
-    <t>Matthew Rubio</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>Right seat.</t>
-  </si>
-  <si>
-    <t>Cynthia Kim</t>
-  </si>
-  <si>
-    <t>1995</t>
-  </si>
-  <si>
-    <t>Factor daughter right none type.</t>
-  </si>
-  <si>
-    <t>John Grimes</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>Shoulder collection think.</t>
-  </si>
-  <si>
-    <t>Mr. Troy Johnson MD</t>
-  </si>
-  <si>
-    <t>Father kitchen.</t>
-  </si>
-  <si>
-    <t>Mathew Salazar</t>
-  </si>
-  <si>
-    <t>1973</t>
-  </si>
-  <si>
-    <t>Model beyond message.</t>
-  </si>
-  <si>
-    <t>Ruben Maldonado</t>
-  </si>
-  <si>
-    <t>1971</t>
-  </si>
-  <si>
-    <t>Occur every able.</t>
-  </si>
-  <si>
-    <t>Joshua Welch</t>
-  </si>
-  <si>
-    <t>Third interesting trial audience.</t>
-  </si>
-  <si>
-    <t>Gabrielle Kerr</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>Change surface million party style.</t>
-  </si>
-  <si>
-    <t>Paul Bennett</t>
-  </si>
-  <si>
-    <t>Act baby pay.</t>
-  </si>
-  <si>
-    <t>Alexis Jones</t>
+    <t>Strategy value believe.</t>
+  </si>
+  <si>
+    <t>Adam Gutierrez</t>
+  </si>
+  <si>
+    <t>Data who.</t>
+  </si>
+  <si>
+    <t>Michael Grant</t>
+  </si>
+  <si>
+    <t>Dark ever term.</t>
+  </si>
+  <si>
+    <t>Jennifer Sanchez</t>
+  </si>
+  <si>
+    <t>Travel ask view book.</t>
+  </si>
+  <si>
+    <t>Michael Greene</t>
+  </si>
+  <si>
+    <t>Identify former.</t>
+  </si>
+  <si>
+    <t>Anna Byrd</t>
+  </si>
+  <si>
+    <t>Model reach bill beautiful reality.</t>
+  </si>
+  <si>
+    <t>Dominique Moore</t>
+  </si>
+  <si>
+    <t>So guy their each.</t>
+  </si>
+  <si>
+    <t>Sarah Willis</t>
+  </si>
+  <si>
+    <t>Us maybe visit.</t>
+  </si>
+  <si>
+    <t>Jonathan Clark</t>
+  </si>
+  <si>
+    <t>Around up page off president.</t>
+  </si>
+  <si>
+    <t>Alexander Gonzalez</t>
+  </si>
+  <si>
+    <t>Involve last.</t>
+  </si>
+  <si>
+    <t>Mark Klein</t>
   </si>
   <si>
     <t>1990</t>
   </si>
   <si>
-    <t>Myself step everything big down.</t>
-  </si>
-  <si>
-    <t>Hailey Duarte</t>
-  </si>
-  <si>
-    <t>1986</t>
-  </si>
-  <si>
-    <t>Wear have first worry similar.</t>
-  </si>
-  <si>
-    <t>Nicholas Johnson Jr.</t>
-  </si>
-  <si>
-    <t>1998</t>
-  </si>
-  <si>
-    <t>Force fish black.</t>
-  </si>
-  <si>
-    <t>Jorge Snyder</t>
-  </si>
-  <si>
-    <t>1997</t>
-  </si>
-  <si>
-    <t>Prepare several take which.</t>
-  </si>
-  <si>
-    <t>Jennifer Ware</t>
-  </si>
-  <si>
-    <t>1992</t>
-  </si>
-  <si>
-    <t>Fund goal foreign season.</t>
-  </si>
-  <si>
-    <t>Jeffery Houston</t>
-  </si>
-  <si>
-    <t>By ask.</t>
-  </si>
-  <si>
-    <t>Andrew Turner</t>
-  </si>
-  <si>
-    <t>1972</t>
-  </si>
-  <si>
-    <t>Run oil memory.</t>
-  </si>
-  <si>
-    <t>Robert Baird</t>
-  </si>
-  <si>
-    <t>Nice author hot hit.</t>
-  </si>
-  <si>
-    <t>Adrian Smith</t>
-  </si>
-  <si>
-    <t>Less score each their.</t>
-  </si>
-  <si>
-    <t>James Webb</t>
-  </si>
-  <si>
-    <t>Color generation.</t>
-  </si>
-  <si>
-    <t>Matthew May</t>
-  </si>
-  <si>
-    <t>Day later serve.</t>
-  </si>
-  <si>
-    <t>Stephanie Cherry</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>Will since.</t>
-  </si>
-  <si>
-    <t>Timothy Newman</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>Think but manage kitchen.</t>
-  </si>
-  <si>
-    <t>Amy Potter</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>Service another pressure long edge.</t>
-  </si>
-  <si>
-    <t>Jody Clark</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>Investment but second.</t>
-  </si>
-  <si>
-    <t>Yvonne Rodriguez</t>
-  </si>
-  <si>
-    <t>Again relationship another.</t>
-  </si>
-  <si>
-    <t>Heidi Hicks</t>
-  </si>
-  <si>
-    <t>1979</t>
-  </si>
-  <si>
-    <t>Son get usually size.</t>
-  </si>
-  <si>
-    <t>Lauren Clark</t>
-  </si>
-  <si>
-    <t>Develop manage she quality.</t>
-  </si>
-  <si>
-    <t>Mathew Henderson</t>
-  </si>
-  <si>
-    <t>Expect civil sometimes.</t>
-  </si>
-  <si>
-    <t>Melissa Clark</t>
-  </si>
-  <si>
-    <t>Describe friend light certain.</t>
-  </si>
-  <si>
-    <t>Robert Marshall</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>Gas force leader word pattern.</t>
-  </si>
-  <si>
-    <t>James Nguyen</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>Fire about line draw.</t>
-  </si>
-  <si>
-    <t>Pamela Brown</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>Pull parent service network.</t>
-  </si>
-  <si>
-    <t>Dominique Arellano</t>
-  </si>
-  <si>
-    <t>1987</t>
-  </si>
-  <si>
-    <t>Particularly market order.</t>
-  </si>
-  <si>
-    <t>Stephanie Yoder</t>
-  </si>
-  <si>
-    <t>Small to agreement president edge.</t>
-  </si>
-  <si>
-    <t>Matthew Boyer</t>
-  </si>
-  <si>
-    <t>Analysis letter so well could.</t>
-  </si>
-  <si>
-    <t>Christine Martin</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>Head us song glass.</t>
-  </si>
-  <si>
-    <t>Eric Knight</t>
-  </si>
-  <si>
-    <t>Dream three.</t>
-  </si>
-  <si>
-    <t>Laura Hartman</t>
+    <t>Easy among fine.</t>
+  </si>
+  <si>
+    <t>Daniel Church</t>
+  </si>
+  <si>
+    <t>Street tough name.</t>
+  </si>
+  <si>
+    <t>Kelsey Robbins</t>
+  </si>
+  <si>
+    <t>Do land keep life.</t>
+  </si>
+  <si>
+    <t>Jesus Jones</t>
   </si>
   <si>
     <t>1999</t>
   </si>
   <si>
-    <t>Hot language however blood player.</t>
-  </si>
-  <si>
-    <t>Stephanie Miller</t>
-  </si>
-  <si>
-    <t>Audience there.</t>
-  </si>
-  <si>
-    <t>Amanda Williams</t>
-  </si>
-  <si>
-    <t>Move case.</t>
-  </si>
-  <si>
-    <t>Tammy Jordan</t>
-  </si>
-  <si>
-    <t>A full fine model more.</t>
-  </si>
-  <si>
-    <t>Sophia Horton</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>Control much run institution.</t>
-  </si>
-  <si>
-    <t>Sandra Douglas</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>Speech simply sort.</t>
-  </si>
-  <si>
-    <t>Paul Burnett</t>
-  </si>
-  <si>
-    <t>1984</t>
-  </si>
-  <si>
-    <t>Whether politics training experience.</t>
-  </si>
-  <si>
-    <t>Jill Harvey</t>
-  </si>
-  <si>
-    <t>Cause power four.</t>
-  </si>
-  <si>
-    <t>Brittany Perez</t>
-  </si>
-  <si>
-    <t>Material finally into better.</t>
-  </si>
-  <si>
-    <t>Jessica Oliver</t>
-  </si>
-  <si>
-    <t>Air true out reflect.</t>
-  </si>
-  <si>
-    <t>Stacey Johnson</t>
-  </si>
-  <si>
-    <t>Although guess race page result.</t>
-  </si>
-  <si>
-    <t>Thomas Wright</t>
-  </si>
-  <si>
-    <t>Nature back smile.</t>
-  </si>
-  <si>
-    <t>Allen Harris</t>
-  </si>
-  <si>
-    <t>Collection how bag big.</t>
-  </si>
-  <si>
-    <t>Dale Blackburn</t>
-  </si>
-  <si>
-    <t>Nor issue edge pattern.</t>
-  </si>
-  <si>
-    <t>Amy Fitzpatrick</t>
-  </si>
-  <si>
-    <t>Wrong smile live interesting.</t>
-  </si>
-  <si>
-    <t>Gregory Mccormick</t>
-  </si>
-  <si>
-    <t>Too have pass through.</t>
-  </si>
-  <si>
-    <t>Melissa Kelley</t>
-  </si>
-  <si>
-    <t>Allow opportunity dinner.</t>
-  </si>
-  <si>
-    <t>Ruben Stewart</t>
-  </si>
-  <si>
-    <t>Fine cause daughter half region.</t>
-  </si>
-  <si>
-    <t>Ryan Flynn</t>
-  </si>
-  <si>
-    <t>1978</t>
-  </si>
-  <si>
-    <t>Want throw should.</t>
-  </si>
-  <si>
-    <t>Career late term.</t>
-  </si>
-  <si>
-    <t>Stefanie Manning</t>
-  </si>
-  <si>
-    <t>Minute training cover.</t>
-  </si>
-  <si>
-    <t>Johnny Brewer</t>
-  </si>
-  <si>
-    <t>Expect economic natural.</t>
-  </si>
-  <si>
-    <t>James Fletcher</t>
-  </si>
-  <si>
-    <t>1996</t>
-  </si>
-  <si>
-    <t>Science my population.</t>
-  </si>
-  <si>
-    <t>Julie Williams</t>
-  </si>
-  <si>
-    <t>Office kind mission change interesting.</t>
-  </si>
-  <si>
-    <t>Shannon Harrell DVM</t>
-  </si>
-  <si>
-    <t>Simply health item former.</t>
-  </si>
-  <si>
-    <t>Brad Lin</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>Reveal whose leave.</t>
-  </si>
-  <si>
-    <t>Lauren Gregory</t>
-  </si>
-  <si>
-    <t>This include price.</t>
-  </si>
-  <si>
-    <t>Andrew Brown</t>
-  </si>
-  <si>
-    <t>May nation large support ago.</t>
-  </si>
-  <si>
-    <t>Mark Perkins</t>
-  </si>
-  <si>
-    <t>1975</t>
-  </si>
-  <si>
-    <t>Feel himself court every.</t>
-  </si>
-  <si>
-    <t>Tracy Murphy</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>Thing television generation let.</t>
-  </si>
-  <si>
-    <t>Kristen Cameron</t>
-  </si>
-  <si>
-    <t>1993</t>
-  </si>
-  <si>
-    <t>Actually process improve back.</t>
-  </si>
-  <si>
-    <t>Sarah Shea</t>
-  </si>
-  <si>
-    <t>Many must cultural have.</t>
-  </si>
-  <si>
-    <t>James Frazier</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>Use public.</t>
-  </si>
-  <si>
-    <t>Joanna Moreno</t>
-  </si>
-  <si>
-    <t>Soon though.</t>
-  </si>
-  <si>
-    <t>Todd Werner</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>Reveal executive worker police.</t>
-  </si>
-  <si>
-    <t>Jacqueline Huffman</t>
-  </si>
-  <si>
-    <t>1980</t>
-  </si>
-  <si>
-    <t>Car particularly.</t>
-  </si>
-  <si>
-    <t>Kyle Leach</t>
-  </si>
-  <si>
-    <t>Country sing.</t>
-  </si>
-  <si>
-    <t>William Ray</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>Week support.</t>
-  </si>
-  <si>
-    <t>Robin Green</t>
-  </si>
-  <si>
-    <t>Although black.</t>
-  </si>
-  <si>
-    <t>Patricia Gardner</t>
-  </si>
-  <si>
-    <t>1974</t>
-  </si>
-  <si>
-    <t>Computer rule big star.</t>
-  </si>
-  <si>
-    <t>Kelly Galloway</t>
-  </si>
-  <si>
-    <t>Group billion.</t>
-  </si>
-  <si>
-    <t>Jennifer Wright</t>
-  </si>
-  <si>
-    <t>Professor better development.</t>
-  </si>
-  <si>
-    <t>Ryan Woodward</t>
-  </si>
-  <si>
-    <t>Include surface per.</t>
-  </si>
-  <si>
-    <t>Jonathan Harvey</t>
-  </si>
-  <si>
-    <t>Heart development.</t>
-  </si>
-  <si>
-    <t>Sarah Ford</t>
-  </si>
-  <si>
-    <t>1970</t>
-  </si>
-  <si>
-    <t>Thousand serious experience take dark.</t>
-  </si>
-  <si>
-    <t>Christopher Howard</t>
-  </si>
-  <si>
-    <t>Statement according car.</t>
-  </si>
-  <si>
-    <t>Nicole Berry</t>
-  </si>
-  <si>
-    <t>Change modern.</t>
-  </si>
-  <si>
-    <t>Michael Boyer</t>
-  </si>
-  <si>
-    <t>1991</t>
-  </si>
-  <si>
-    <t>Set entire institution drop.</t>
-  </si>
-  <si>
-    <t>Sabrina Bishop</t>
-  </si>
-  <si>
-    <t>Leave not.</t>
-  </si>
-  <si>
-    <t>Michael Thompson</t>
-  </si>
-  <si>
-    <t>Green road.</t>
-  </si>
-  <si>
-    <t>Chris Wilkerson</t>
-  </si>
-  <si>
-    <t>Service man admit.</t>
-  </si>
-  <si>
-    <t>Joel Barber</t>
-  </si>
-  <si>
-    <t>Research finally fish paper.</t>
-  </si>
-  <si>
-    <t>April Alvarado</t>
-  </si>
-  <si>
-    <t>At food hold.</t>
-  </si>
-  <si>
-    <t>David Logan</t>
-  </si>
-  <si>
-    <t>Nothing reveal set evidence there.</t>
-  </si>
-  <si>
-    <t>Andrea Page</t>
-  </si>
-  <si>
-    <t>Sea somebody character join.</t>
-  </si>
-  <si>
-    <t>Miss Morgan Griffin</t>
-  </si>
-  <si>
-    <t>Hard sell mean.</t>
-  </si>
-  <si>
-    <t>Cole Cook</t>
-  </si>
-  <si>
-    <t>Agreement pull rock very development.</t>
-  </si>
-  <si>
-    <t>Matthew Jones</t>
-  </si>
-  <si>
-    <t>Evidence just author same.</t>
-  </si>
-  <si>
-    <t>Brian Silva</t>
-  </si>
-  <si>
-    <t>Talk once recognize.</t>
-  </si>
-  <si>
-    <t>Paula Maddox</t>
-  </si>
-  <si>
-    <t>But process cut suddenly factor.</t>
-  </si>
-  <si>
-    <t>John Hickman</t>
-  </si>
-  <si>
-    <t>Peace determine we.</t>
-  </si>
-  <si>
-    <t>Charlotte Costa</t>
-  </si>
-  <si>
-    <t>Effect local purpose every.</t>
-  </si>
-  <si>
-    <t>Tamara Richardson</t>
-  </si>
-  <si>
-    <t>There store.</t>
-  </si>
-  <si>
-    <t>Robin Young</t>
-  </si>
-  <si>
-    <t>Huge require.</t>
-  </si>
-  <si>
-    <t>Joshua Gibson</t>
-  </si>
-  <si>
-    <t>Expert report information even.</t>
-  </si>
-  <si>
-    <t>Say not too.</t>
-  </si>
-  <si>
-    <t>Maria Williams</t>
-  </si>
-  <si>
-    <t>Near guy condition.</t>
-  </si>
-  <si>
-    <t>Shannon Johnson</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>Yourself not place fine.</t>
-  </si>
-  <si>
-    <t>Charles Werner</t>
-  </si>
-  <si>
-    <t>Owner audience spring president space.</t>
-  </si>
-  <si>
-    <t>Annette Leon</t>
-  </si>
-  <si>
-    <t>Quality structure seven.</t>
-  </si>
-  <si>
-    <t>Jordan Jenkins</t>
-  </si>
-  <si>
-    <t>Skill majority another.</t>
-  </si>
-  <si>
-    <t>Christopher Gordon</t>
-  </si>
-  <si>
-    <t>Choose subject.</t>
-  </si>
-  <si>
-    <t>Danielle Le</t>
-  </si>
-  <si>
-    <t>Question work night.</t>
-  </si>
-  <si>
-    <t>Sarah Carpenter</t>
-  </si>
-  <si>
-    <t>1981</t>
-  </si>
-  <si>
-    <t>Plant director increase decide one.</t>
-  </si>
-  <si>
-    <t>John Bishop</t>
-  </si>
-  <si>
-    <t>Democratic produce together material.</t>
-  </si>
-  <si>
-    <t>Rachel Davis</t>
-  </si>
-  <si>
-    <t>Six who middle.</t>
-  </si>
-  <si>
-    <t>Joshua Reeves</t>
-  </si>
-  <si>
-    <t>Hair tax.</t>
-  </si>
-  <si>
-    <t>Traci Scott</t>
-  </si>
-  <si>
-    <t>1976</t>
-  </si>
-  <si>
-    <t>Less respond write lose.</t>
-  </si>
-  <si>
-    <t>Jesse Delgado</t>
-  </si>
-  <si>
-    <t>Time if election.</t>
-  </si>
-  <si>
-    <t>Alicia Bennett</t>
-  </si>
-  <si>
-    <t>Seek wish project.</t>
-  </si>
-  <si>
-    <t>Elizabeth Ryan</t>
-  </si>
-  <si>
-    <t>1989</t>
-  </si>
-  <si>
-    <t>Stand between.</t>
-  </si>
-  <si>
-    <t>Chad Hall</t>
-  </si>
-  <si>
-    <t>Protect democratic.</t>
-  </si>
-  <si>
-    <t>Ray Bryant DDS</t>
-  </si>
-  <si>
-    <t>Strategy value believe.</t>
-  </si>
-  <si>
-    <t>Adam Gutierrez</t>
-  </si>
-  <si>
-    <t>Data who.</t>
-  </si>
-  <si>
-    <t>Michael Grant</t>
-  </si>
-  <si>
-    <t>Dark ever term.</t>
-  </si>
-  <si>
-    <t>Jennifer Sanchez</t>
-  </si>
-  <si>
-    <t>Travel ask view book.</t>
-  </si>
-  <si>
-    <t>Michael Greene</t>
-  </si>
-  <si>
-    <t>1988</t>
-  </si>
-  <si>
-    <t>Identify former.</t>
-  </si>
-  <si>
-    <t>Anna Byrd</t>
-  </si>
-  <si>
-    <t>Model reach bill beautiful reality.</t>
-  </si>
-  <si>
-    <t>Dominique Moore</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>So guy their each.</t>
-  </si>
-  <si>
-    <t>Sarah Willis</t>
-  </si>
-  <si>
-    <t>Us maybe visit.</t>
-  </si>
-  <si>
-    <t>Jonathan Clark</t>
-  </si>
-  <si>
-    <t>Around up page off president.</t>
-  </si>
-  <si>
-    <t>Alexander Gonzalez</t>
-  </si>
-  <si>
-    <t>Involve last.</t>
-  </si>
-  <si>
-    <t>Mark Klein</t>
-  </si>
-  <si>
-    <t>Easy among fine.</t>
-  </si>
-  <si>
-    <t>Daniel Church</t>
-  </si>
-  <si>
-    <t>Street tough name.</t>
-  </si>
-  <si>
-    <t>Kelsey Robbins</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>Do land keep life.</t>
-  </si>
-  <si>
-    <t>Jesus Jones</t>
-  </si>
-  <si>
     <t>Sometimes end product feel.</t>
   </si>
   <si>
@@ -1065,6 +918,9 @@
     <t>George Russell</t>
   </si>
   <si>
+    <t>1994</t>
+  </si>
+  <si>
     <t>Race campaign those despite.</t>
   </si>
   <si>
@@ -1083,9 +939,6 @@
     <t>Eric Gonzalez</t>
   </si>
   <si>
-    <t>1994</t>
-  </si>
-  <si>
     <t>Tell during hospital.</t>
   </si>
   <si>
@@ -1128,9 +981,6 @@
     <t>Kelly Hall</t>
   </si>
   <si>
-    <t>1982</t>
-  </si>
-  <si>
     <t>Enjoy shake talk.</t>
   </si>
   <si>
@@ -1153,6 +1003,72 @@
   </si>
   <si>
     <t>Nicole Alexander</t>
+  </si>
+  <si>
+    <t>In person center.</t>
+  </si>
+  <si>
+    <t>Richard Long</t>
+  </si>
+  <si>
+    <t>And past bad democratic.</t>
+  </si>
+  <si>
+    <t>Jaclyn Davidson</t>
+  </si>
+  <si>
+    <t>Foot option dinner act statement.</t>
+  </si>
+  <si>
+    <t>Christopher Jones</t>
+  </si>
+  <si>
+    <t>Generation community budget tonight focus.</t>
+  </si>
+  <si>
+    <t>John Petty</t>
+  </si>
+  <si>
+    <t>Choice any design win.</t>
+  </si>
+  <si>
+    <t>Lauren Chambers</t>
+  </si>
+  <si>
+    <t>Main dream building.</t>
+  </si>
+  <si>
+    <t>Christopher Dalton</t>
+  </si>
+  <si>
+    <t>Century century drop.</t>
+  </si>
+  <si>
+    <t>Michael Rogers</t>
+  </si>
+  <si>
+    <t>Whose even.</t>
+  </si>
+  <si>
+    <t>Isaac Henderson</t>
+  </si>
+  <si>
+    <t>Include citizen partner book figure.</t>
+  </si>
+  <si>
+    <t>Rachel Gutierrez</t>
+  </si>
+  <si>
+    <t>Together long.</t>
+  </si>
+  <si>
+    <t>Shawn Avila</t>
+  </si>
+  <si>
+    <t>Reality despite fact.</t>
+  </si>
+  <si>
+    <t>Spencer Thomas</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.6328125" customWidth="1"/>
@@ -1535,84 +1451,81 @@
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" t="s">
-        <v>24</v>
-      </c>
       <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1623,10 +1536,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
         <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -1637,10 +1550,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
         <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -1651,10 +1564,10 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
         <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1665,94 +1578,94 @@
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1763,136 +1676,136 @@
         <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" t="s">
         <v>56</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
         <v>57</v>
-      </c>
-      <c r="C20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" t="s">
         <v>59</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
         <v>60</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" t="s">
         <v>62</v>
       </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
         <v>65</v>
-      </c>
-      <c r="B23" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s">
         <v>67</v>
       </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C25" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
         <v>74</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" t="s">
         <v>76</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
         <v>77</v>
-      </c>
-      <c r="C28" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1903,108 +1816,108 @@
         <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" t="s">
         <v>81</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
         <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
         <v>84</v>
       </c>
-      <c r="B31" t="s">
-        <v>85</v>
-      </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>89</v>
+        <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
         <v>92</v>
-      </c>
-      <c r="B34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
         <v>95</v>
-      </c>
-      <c r="B35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" t="s">
         <v>97</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
         <v>98</v>
-      </c>
-      <c r="C36" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -2015,24 +1928,24 @@
         <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -2043,10 +1956,10 @@
         <v>105</v>
       </c>
       <c r="C39" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
         <v>106</v>
-      </c>
-      <c r="D39" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -2057,136 +1970,136 @@
         <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>109</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B42" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" t="s">
         <v>115</v>
-      </c>
-      <c r="B43" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" t="s">
-        <v>25</v>
-      </c>
-      <c r="D43" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>116</v>
+      </c>
+      <c r="B44" t="s">
         <v>117</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
         <v>118</v>
-      </c>
-      <c r="C44" t="s">
-        <v>119</v>
-      </c>
-      <c r="D44" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>119</v>
+      </c>
+      <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="B45" t="s">
-        <v>121</v>
-      </c>
       <c r="C45" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>121</v>
+      </c>
+      <c r="B46" t="s">
         <v>122</v>
       </c>
-      <c r="B46" t="s">
-        <v>123</v>
-      </c>
       <c r="C46" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
+        <v>126</v>
+      </c>
+      <c r="C48" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
         <v>127</v>
-      </c>
-      <c r="B48" t="s">
-        <v>128</v>
-      </c>
-      <c r="C48" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>128</v>
+      </c>
+      <c r="B49" t="s">
         <v>129</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
         <v>130</v>
-      </c>
-      <c r="C49" t="s">
-        <v>22</v>
-      </c>
-      <c r="D49" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2197,10 +2110,10 @@
         <v>132</v>
       </c>
       <c r="C50" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
         <v>133</v>
-      </c>
-      <c r="D50" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -2211,10 +2124,10 @@
         <v>135</v>
       </c>
       <c r="C51" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
         <v>136</v>
-      </c>
-      <c r="D51" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2225,24 +2138,24 @@
         <v>138</v>
       </c>
       <c r="C52" t="s">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" t="s">
         <v>140</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" t="s">
         <v>141</v>
-      </c>
-      <c r="C53" t="s">
-        <v>136</v>
-      </c>
-      <c r="D53" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2253,472 +2166,472 @@
         <v>143</v>
       </c>
       <c r="C54" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B56" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B57" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B58" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C58" t="s">
         <v>6</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B59" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B61" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C61" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>161</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B62" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C62" t="s">
-        <v>133</v>
+        <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>7</v>
+        <v>164</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C63" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B64" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C64" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="D64" t="s">
-        <v>7</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="C65" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B66" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C66" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B67" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C67" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D67" t="s">
-        <v>7</v>
+        <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C68" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B70" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C70" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D70" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>186</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B72" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C72" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>7</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B73" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C73" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C74" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
       <c r="D74" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B75" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C75" t="s">
-        <v>189</v>
+        <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B76" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C76" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B77" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C77" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B78" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C78" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B80" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C80" t="s">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B81" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C81" t="s">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="D81" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B82" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C82" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B83" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C83" t="s">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="D83" t="s">
-        <v>7</v>
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B84" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C84" t="s">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B85" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C85" t="s">
-        <v>215</v>
+        <v>6</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B86" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C86" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>48</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>106</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
@@ -2729,10 +2642,10 @@
         <v>221</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -2743,66 +2656,66 @@
         <v>223</v>
       </c>
       <c r="C89" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>7</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B90" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C90" t="s">
-        <v>226</v>
+        <v>6</v>
       </c>
       <c r="D90" t="s">
-        <v>7</v>
+        <v>227</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B91" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C91" t="s">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
+        <v>224</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B92" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C92" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B93" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C93" t="s">
-        <v>233</v>
+        <v>6</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
@@ -2813,654 +2726,654 @@
         <v>235</v>
       </c>
       <c r="C94" t="s">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="D94" t="s">
-        <v>7</v>
+        <v>236</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B95" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C95" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B96" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C96" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B97" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C97" t="s">
-        <v>215</v>
+        <v>6</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B98" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C98" t="s">
-        <v>233</v>
+        <v>6</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B99" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C99" t="s">
-        <v>233</v>
+        <v>6</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B100" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C100" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="D100" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B101" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C101" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B102" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C102" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B103" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C103" t="s">
-        <v>192</v>
+        <v>6</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B104" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C104" t="s">
-        <v>86</v>
+        <v>6</v>
       </c>
       <c r="D104" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B105" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C105" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B106" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C106" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="D106" t="s">
-        <v>7</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B107" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C107" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B108" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C108" t="s">
-        <v>119</v>
+        <v>6</v>
       </c>
       <c r="D108" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B109" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C109" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="D109" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B110" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C110" t="s">
-        <v>164</v>
+        <v>6</v>
       </c>
       <c r="D110" t="s">
-        <v>7</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B111" t="s">
-        <v>108</v>
+        <v>272</v>
       </c>
       <c r="C111" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B112" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C112" t="s">
-        <v>233</v>
+        <v>6</v>
       </c>
       <c r="D112" t="s">
-        <v>7</v>
+        <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B113" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C113" t="s">
-        <v>273</v>
+        <v>6</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>164</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B114" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C114" t="s">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="D114" t="s">
-        <v>7</v>
+        <v>279</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B115" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C115" t="s">
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B116" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C116" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="D116" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B117" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C117" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="D117" t="s">
-        <v>7</v>
+        <v>286</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B118" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C118" t="s">
-        <v>226</v>
+        <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>7</v>
+        <v>174</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B119" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C119" t="s">
-        <v>286</v>
+        <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>7</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B120" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="C120" t="s">
-        <v>226</v>
+        <v>6</v>
       </c>
       <c r="D120" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B121" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C121" t="s">
-        <v>286</v>
+        <v>6</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B122" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C122" t="s">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>239</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B123" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C123" t="s">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>299</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B124" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C124" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B125" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C125" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D125" t="s">
-        <v>7</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="B126" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C126" t="s">
-        <v>302</v>
+        <v>6</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>236</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B127" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C127" t="s">
-        <v>210</v>
+        <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>191</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B128" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C128" t="s">
-        <v>295</v>
+        <v>6</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B129" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C129" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B130" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C130" t="s">
-        <v>202</v>
+        <v>6</v>
       </c>
       <c r="D130" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B131" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C131" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="D131" t="s">
-        <v>7</v>
+        <v>204</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B132" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C132" t="s">
-        <v>315</v>
+        <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B133" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C133" t="s">
-        <v>103</v>
+        <v>6</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>156</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B134" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C134" t="s">
-        <v>320</v>
+        <v>6</v>
       </c>
       <c r="D134" t="s">
-        <v>7</v>
+        <v>130</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B135" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C135" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D135" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B136" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C136" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>136</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B137" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C137" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>7</v>
+        <v>204</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B138" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C138" t="s">
-        <v>197</v>
+        <v>6</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>92</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B139" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C139" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>7</v>
+        <v>74</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B140" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C140" t="s">
-        <v>333</v>
+        <v>6</v>
       </c>
       <c r="D140" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
@@ -3471,10 +3384,10 @@
         <v>335</v>
       </c>
       <c r="C141" t="s">
-        <v>172</v>
+        <v>6</v>
       </c>
       <c r="D141" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
@@ -3485,10 +3398,10 @@
         <v>337</v>
       </c>
       <c r="C142" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
@@ -3499,10 +3412,10 @@
         <v>339</v>
       </c>
       <c r="C143" t="s">
-        <v>273</v>
+        <v>6</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
@@ -3513,10 +3426,10 @@
         <v>341</v>
       </c>
       <c r="C144" t="s">
-        <v>333</v>
+        <v>6</v>
       </c>
       <c r="D144" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
@@ -3527,10 +3440,10 @@
         <v>343</v>
       </c>
       <c r="C145" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
       <c r="D145" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
@@ -3541,10 +3454,10 @@
         <v>345</v>
       </c>
       <c r="C146" t="s">
-        <v>333</v>
+        <v>6</v>
       </c>
       <c r="D146" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
@@ -3555,10 +3468,10 @@
         <v>347</v>
       </c>
       <c r="C147" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="D147" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
@@ -3569,192 +3482,10 @@
         <v>349</v>
       </c>
       <c r="C148" t="s">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="D148" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>350</v>
-      </c>
-      <c r="B149" t="s">
-        <v>351</v>
-      </c>
-      <c r="C149" t="s">
-        <v>315</v>
-      </c>
-      <c r="D149" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>352</v>
-      </c>
-      <c r="B150" t="s">
-        <v>353</v>
-      </c>
-      <c r="C150" t="s">
-        <v>354</v>
-      </c>
-      <c r="D150" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>355</v>
-      </c>
-      <c r="B151" t="s">
-        <v>356</v>
-      </c>
-      <c r="C151" t="s">
-        <v>133</v>
-      </c>
-      <c r="D151" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>357</v>
-      </c>
-      <c r="B152" t="s">
-        <v>358</v>
-      </c>
-      <c r="C152" t="s">
-        <v>61</v>
-      </c>
-      <c r="D152" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>359</v>
-      </c>
-      <c r="B153" t="s">
-        <v>360</v>
-      </c>
-      <c r="C153" t="s">
-        <v>94</v>
-      </c>
-      <c r="D153" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>361</v>
-      </c>
-      <c r="B154" t="s">
-        <v>362</v>
-      </c>
-      <c r="C154" t="s">
-        <v>179</v>
-      </c>
-      <c r="D154" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>363</v>
-      </c>
-      <c r="B155" t="s">
-        <v>364</v>
-      </c>
-      <c r="C155" t="s">
-        <v>22</v>
-      </c>
-      <c r="D155" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>365</v>
-      </c>
-      <c r="B156" t="s">
-        <v>366</v>
-      </c>
-      <c r="C156" t="s">
-        <v>94</v>
-      </c>
-      <c r="D156" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>367</v>
-      </c>
-      <c r="B157" t="s">
-        <v>368</v>
-      </c>
-      <c r="C157" t="s">
-        <v>369</v>
-      </c>
-      <c r="D157" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>370</v>
-      </c>
-      <c r="B158" t="s">
-        <v>371</v>
-      </c>
-      <c r="C158" t="s">
-        <v>210</v>
-      </c>
-      <c r="D158" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A159" t="s">
-        <v>372</v>
-      </c>
-      <c r="B159" t="s">
-        <v>373</v>
-      </c>
-      <c r="C159" t="s">
-        <v>80</v>
-      </c>
-      <c r="D159" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A160" t="s">
-        <v>374</v>
-      </c>
-      <c r="B160" t="s">
-        <v>375</v>
-      </c>
-      <c r="C160" t="s">
-        <v>273</v>
-      </c>
-      <c r="D160" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A161" t="s">
-        <v>376</v>
-      </c>
-      <c r="B161" t="s">
-        <v>377</v>
-      </c>
-      <c r="C161" t="s">
-        <v>109</v>
-      </c>
-      <c r="D161" t="s">
-        <v>7</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/storage/Librarie_Saint_Laurent.xlsx
+++ b/storage/Librarie_Saint_Laurent.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Information_Librarie_SL" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="373">
   <si>
     <t>Book_name</t>
   </si>
@@ -27,10 +27,13 @@
     <t>Author_name</t>
   </si>
   <si>
+    <t>Publication_Year</t>
+  </si>
+  <si>
     <t>Reviews</t>
   </si>
   <si>
-    <t>Publication_Year</t>
+    <t>Number of available books</t>
   </si>
   <si>
     <t>Opportunity crime degree.</t>
@@ -39,966 +42,966 @@
     <t>James Vazquez</t>
   </si>
   <si>
+    <t>2013</t>
+  </si>
+  <si>
     <t>No reviews yet</t>
   </si>
   <si>
+    <t>Wide cultural season follow culture.</t>
+  </si>
+  <si>
+    <t>Unkown Author</t>
+  </si>
+  <si>
+    <t>1984</t>
+  </si>
+  <si>
+    <t>Color generation.</t>
+  </si>
+  <si>
+    <t>Matthew May</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>Day later serve.</t>
+  </si>
+  <si>
+    <t>Stephanie Cherry</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>Will since.</t>
+  </si>
+  <si>
+    <t>Timothy Newman</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>Think but manage kitchen.</t>
+  </si>
+  <si>
+    <t>Amy Potter</t>
+  </si>
+  <si>
+    <t>1987</t>
+  </si>
+  <si>
+    <t>Service another pressure long edge.</t>
+  </si>
+  <si>
+    <t>Jody Clark</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>Investment but second.</t>
+  </si>
+  <si>
+    <t>Yvonne Rodriguez</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Again relationship another.</t>
+  </si>
+  <si>
+    <t>Heidi Hicks</t>
+  </si>
+  <si>
+    <t>1971</t>
+  </si>
+  <si>
+    <t>Son get usually size.</t>
+  </si>
+  <si>
+    <t>Lauren Clark</t>
+  </si>
+  <si>
+    <t>1977</t>
+  </si>
+  <si>
+    <t>Develop manage she quality.</t>
+  </si>
+  <si>
+    <t>Mathew Henderson</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>Expect civil sometimes.</t>
+  </si>
+  <si>
+    <t>Melissa Clark</t>
+  </si>
+  <si>
+    <t>1972</t>
+  </si>
+  <si>
+    <t>Things we never got over</t>
+  </si>
+  <si>
+    <t>Colleen Hoover</t>
+  </si>
+  <si>
+    <t>Gas force leader word pattern.</t>
+  </si>
+  <si>
+    <t>James Nguyen</t>
+  </si>
+  <si>
+    <t>1981</t>
+  </si>
+  <si>
+    <t>Fire about line draw.</t>
+  </si>
+  <si>
+    <t>Pamela Brown</t>
+  </si>
+  <si>
+    <t>1983</t>
+  </si>
+  <si>
+    <t>Pull parent service network.</t>
+  </si>
+  <si>
+    <t>Dominique Arellano</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>Particularly market order.</t>
+  </si>
+  <si>
+    <t>Stephanie Yoder</t>
+  </si>
+  <si>
+    <t>1980</t>
+  </si>
+  <si>
+    <t>Small to agreement president edge.</t>
+  </si>
+  <si>
+    <t>Matthew Boyer</t>
+  </si>
+  <si>
+    <t>1982</t>
+  </si>
+  <si>
+    <t>Analysis letter so well could.</t>
+  </si>
+  <si>
+    <t>Christine Martin</t>
+  </si>
+  <si>
+    <t>Head us song glass.</t>
+  </si>
+  <si>
+    <t>Eric Knight</t>
+  </si>
+  <si>
+    <t>Dream three.</t>
+  </si>
+  <si>
+    <t>Laura Hartman</t>
+  </si>
+  <si>
+    <t>Hot language however blood player.</t>
+  </si>
+  <si>
+    <t>Stephanie Miller</t>
+  </si>
+  <si>
+    <t>1994</t>
+  </si>
+  <si>
+    <t>Audience there.</t>
+  </si>
+  <si>
+    <t>Amanda Williams</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>Move case.</t>
+  </si>
+  <si>
+    <t>Tammy Jordan</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>A full fine model more.</t>
+  </si>
+  <si>
+    <t>Sophia Horton</t>
+  </si>
+  <si>
+    <t>Control much run institution.</t>
+  </si>
+  <si>
+    <t>Sandra Douglas</t>
+  </si>
+  <si>
+    <t>Speech simply sort.</t>
+  </si>
+  <si>
+    <t>Paul Burnett</t>
+  </si>
+  <si>
     <t>2022</t>
   </si>
   <si>
-    <t>Wide cultural season follow culture.</t>
+    <t>Whether politics training experience.</t>
+  </si>
+  <si>
+    <t>Jill Harvey</t>
+  </si>
+  <si>
+    <t>1991</t>
+  </si>
+  <si>
+    <t>Cause power four.</t>
+  </si>
+  <si>
+    <t>Brittany Perez</t>
+  </si>
+  <si>
+    <t>Material finally into better.</t>
+  </si>
+  <si>
+    <t>Jessica Oliver</t>
+  </si>
+  <si>
+    <t>Air true out reflect.</t>
+  </si>
+  <si>
+    <t>Stacey Johnson</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>Although guess race page result.</t>
+  </si>
+  <si>
+    <t>Thomas Wright</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>Nature back smile.</t>
+  </si>
+  <si>
+    <t>Allen Harris</t>
+  </si>
+  <si>
+    <t>1974</t>
+  </si>
+  <si>
+    <t>Collection how bag big.</t>
+  </si>
+  <si>
+    <t>Dale Blackburn</t>
+  </si>
+  <si>
+    <t>1999</t>
+  </si>
+  <si>
+    <t>Nor issue edge pattern.</t>
+  </si>
+  <si>
+    <t>Amy Fitzpatrick</t>
+  </si>
+  <si>
+    <t>1993</t>
+  </si>
+  <si>
+    <t>Wrong smile live interesting.</t>
+  </si>
+  <si>
+    <t>Gregory Mccormick</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>Too have pass through.</t>
+  </si>
+  <si>
+    <t>Melissa Kelley</t>
+  </si>
+  <si>
+    <t>1976</t>
+  </si>
+  <si>
+    <t>Allow opportunity dinner.</t>
+  </si>
+  <si>
+    <t>Ruben Stewart</t>
   </si>
   <si>
     <t>1998</t>
   </si>
   <si>
-    <t>Color generation.</t>
-  </si>
-  <si>
-    <t>Matthew May</t>
-  </si>
-  <si>
-    <t>1976</t>
-  </si>
-  <si>
-    <t>Day later serve.</t>
-  </si>
-  <si>
-    <t>Stephanie Cherry</t>
+    <t>Fine cause daughter half region.</t>
+  </si>
+  <si>
+    <t>Ryan Flynn</t>
+  </si>
+  <si>
+    <t>Want throw should.</t>
+  </si>
+  <si>
+    <t>Robert Marshall</t>
+  </si>
+  <si>
+    <t>1975</t>
+  </si>
+  <si>
+    <t>Career late term.</t>
+  </si>
+  <si>
+    <t>Stefanie Manning</t>
+  </si>
+  <si>
+    <t>Minute training cover.</t>
+  </si>
+  <si>
+    <t>Johnny Brewer</t>
+  </si>
+  <si>
+    <t>Expect economic natural.</t>
+  </si>
+  <si>
+    <t>James Fletcher</t>
+  </si>
+  <si>
+    <t>1978</t>
+  </si>
+  <si>
+    <t>Science my population.</t>
+  </si>
+  <si>
+    <t>Julie Williams</t>
+  </si>
+  <si>
+    <t>1995</t>
+  </si>
+  <si>
+    <t>Office kind mission change interesting.</t>
+  </si>
+  <si>
+    <t>Shannon Harrell DVM</t>
+  </si>
+  <si>
+    <t>1997</t>
+  </si>
+  <si>
+    <t>Simply health item former.</t>
+  </si>
+  <si>
+    <t>Brad Lin</t>
+  </si>
+  <si>
+    <t>Reveal whose leave.</t>
+  </si>
+  <si>
+    <t>Lauren Gregory</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>This include price.</t>
+  </si>
+  <si>
+    <t>Andrew Brown</t>
+  </si>
+  <si>
+    <t>May nation large support ago.</t>
+  </si>
+  <si>
+    <t>Mark Perkins</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Feel himself court every.</t>
+  </si>
+  <si>
+    <t>Tracy Murphy</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Thing television generation let.</t>
+  </si>
+  <si>
+    <t>Kristen Cameron</t>
   </si>
   <si>
     <t>1992</t>
   </si>
   <si>
-    <t>Will since.</t>
-  </si>
-  <si>
-    <t>Timothy Newman</t>
+    <t>Actually process improve back.</t>
+  </si>
+  <si>
+    <t>Sarah Shea</t>
+  </si>
+  <si>
+    <t>Many must cultural have.</t>
+  </si>
+  <si>
+    <t>James Frazier</t>
+  </si>
+  <si>
+    <t>1973</t>
+  </si>
+  <si>
+    <t>Use public.</t>
+  </si>
+  <si>
+    <t>Joanna Moreno</t>
+  </si>
+  <si>
+    <t>Soon though.</t>
+  </si>
+  <si>
+    <t>Todd Werner</t>
+  </si>
+  <si>
+    <t>Reveal executive worker police.</t>
+  </si>
+  <si>
+    <t>Jacqueline Huffman</t>
+  </si>
+  <si>
+    <t>Car particularly.</t>
+  </si>
+  <si>
+    <t>Kyle Leach</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>Country sing.</t>
+  </si>
+  <si>
+    <t>William Ray</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>Week support.</t>
+  </si>
+  <si>
+    <t>Robin Green</t>
+  </si>
+  <si>
+    <t>Although black.</t>
+  </si>
+  <si>
+    <t>Patricia Gardner</t>
+  </si>
+  <si>
+    <t>Computer rule big star.</t>
+  </si>
+  <si>
+    <t>Kelly Galloway</t>
+  </si>
+  <si>
+    <t>Group billion.</t>
+  </si>
+  <si>
+    <t>Jennifer Wright</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>Professor better development.</t>
+  </si>
+  <si>
+    <t>Ryan Woodward</t>
+  </si>
+  <si>
+    <t>Include surface per.</t>
+  </si>
+  <si>
+    <t>Jonathan Harvey</t>
+  </si>
+  <si>
+    <t>Heart development.</t>
+  </si>
+  <si>
+    <t>Sarah Ford</t>
+  </si>
+  <si>
+    <t>Thousand serious experience take dark.</t>
+  </si>
+  <si>
+    <t>Christopher Howard</t>
+  </si>
+  <si>
+    <t>Statement according car.</t>
+  </si>
+  <si>
+    <t>Nicole Berry</t>
+  </si>
+  <si>
+    <t>Change modern.</t>
+  </si>
+  <si>
+    <t>Michael Boyer</t>
+  </si>
+  <si>
+    <t>Set entire institution drop.</t>
+  </si>
+  <si>
+    <t>Sabrina Bishop</t>
+  </si>
+  <si>
+    <t>1970</t>
+  </si>
+  <si>
+    <t>Leave not.</t>
+  </si>
+  <si>
+    <t>Michael Thompson</t>
+  </si>
+  <si>
+    <t>1985</t>
+  </si>
+  <si>
+    <t>Green road.</t>
+  </si>
+  <si>
+    <t>Chris Wilkerson</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>Service man admit.</t>
+  </si>
+  <si>
+    <t>Joel Barber</t>
+  </si>
+  <si>
+    <t>Research finally fish paper.</t>
+  </si>
+  <si>
+    <t>April Alvarado</t>
+  </si>
+  <si>
+    <t>At food hold.</t>
+  </si>
+  <si>
+    <t>David Logan</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>Nothing reveal set evidence there.</t>
+  </si>
+  <si>
+    <t>Andrea Page</t>
+  </si>
+  <si>
+    <t>Sea somebody character join.</t>
+  </si>
+  <si>
+    <t>Miss Morgan Griffin</t>
+  </si>
+  <si>
+    <t>1989</t>
+  </si>
+  <si>
+    <t>Hard sell mean.</t>
+  </si>
+  <si>
+    <t>Cole Cook</t>
+  </si>
+  <si>
+    <t>Agreement pull rock very development.</t>
+  </si>
+  <si>
+    <t>Matthew Jones</t>
+  </si>
+  <si>
+    <t>Evidence just author same.</t>
+  </si>
+  <si>
+    <t>Brian Silva</t>
+  </si>
+  <si>
+    <t>Talk once recognize.</t>
+  </si>
+  <si>
+    <t>Paula Maddox</t>
+  </si>
+  <si>
+    <t>But process cut suddenly factor.</t>
+  </si>
+  <si>
+    <t>John Hickman</t>
+  </si>
+  <si>
+    <t>Peace determine we.</t>
+  </si>
+  <si>
+    <t>Charlotte Costa</t>
+  </si>
+  <si>
+    <t>Effect local purpose every.</t>
+  </si>
+  <si>
+    <t>Tamara Richardson</t>
+  </si>
+  <si>
+    <t>There store.</t>
+  </si>
+  <si>
+    <t>Robin Young</t>
+  </si>
+  <si>
+    <t>Huge require.</t>
+  </si>
+  <si>
+    <t>Joshua Gibson</t>
+  </si>
+  <si>
+    <t>Expert report information even.</t>
+  </si>
+  <si>
+    <t>Say not too.</t>
+  </si>
+  <si>
+    <t>Maria Williams</t>
+  </si>
+  <si>
+    <t>1996</t>
+  </si>
+  <si>
+    <t>Near guy condition.</t>
+  </si>
+  <si>
+    <t>Shannon Johnson</t>
+  </si>
+  <si>
+    <t>Yourself not place fine.</t>
+  </si>
+  <si>
+    <t>Charles Werner</t>
+  </si>
+  <si>
+    <t>Owner audience spring president space.</t>
+  </si>
+  <si>
+    <t>Annette Leon</t>
+  </si>
+  <si>
+    <t>Quality structure seven.</t>
+  </si>
+  <si>
+    <t>Jordan Jenkins</t>
+  </si>
+  <si>
+    <t>Skill majority another.</t>
+  </si>
+  <si>
+    <t>Christopher Gordon</t>
+  </si>
+  <si>
+    <t>Choose subject.</t>
+  </si>
+  <si>
+    <t>Danielle Le</t>
+  </si>
+  <si>
+    <t>Question work night.</t>
+  </si>
+  <si>
+    <t>Sarah Carpenter</t>
+  </si>
+  <si>
+    <t>Plant director increase decide one.</t>
+  </si>
+  <si>
+    <t>John Bishop</t>
+  </si>
+  <si>
+    <t>Democratic produce together material.</t>
+  </si>
+  <si>
+    <t>Rachel Davis</t>
+  </si>
+  <si>
+    <t>Six who middle.</t>
+  </si>
+  <si>
+    <t>Joshua Reeves</t>
+  </si>
+  <si>
+    <t>Hair tax.</t>
+  </si>
+  <si>
+    <t>Traci Scott</t>
+  </si>
+  <si>
+    <t>Less respond write lose.</t>
+  </si>
+  <si>
+    <t>Jesse Delgado</t>
+  </si>
+  <si>
+    <t>Time if election.</t>
+  </si>
+  <si>
+    <t>Alicia Bennett</t>
+  </si>
+  <si>
+    <t>Seek wish project.</t>
+  </si>
+  <si>
+    <t>Elizabeth Ryan</t>
+  </si>
+  <si>
+    <t>Stand between.</t>
+  </si>
+  <si>
+    <t>Chad Hall</t>
+  </si>
+  <si>
+    <t>Protect democratic.</t>
+  </si>
+  <si>
+    <t>Ray Bryant DDS</t>
+  </si>
+  <si>
+    <t>Strategy value believe.</t>
+  </si>
+  <si>
+    <t>Adam Gutierrez</t>
+  </si>
+  <si>
+    <t>Data who.</t>
+  </si>
+  <si>
+    <t>Michael Grant</t>
+  </si>
+  <si>
+    <t>Dark ever term.</t>
+  </si>
+  <si>
+    <t>Jennifer Sanchez</t>
+  </si>
+  <si>
+    <t>Travel ask view book.</t>
+  </si>
+  <si>
+    <t>Michael Greene</t>
+  </si>
+  <si>
+    <t>Identify former.</t>
+  </si>
+  <si>
+    <t>Anna Byrd</t>
+  </si>
+  <si>
+    <t>Model reach bill beautiful reality.</t>
+  </si>
+  <si>
+    <t>Dominique Moore</t>
+  </si>
+  <si>
+    <t>So guy their each.</t>
+  </si>
+  <si>
+    <t>Sarah Willis</t>
+  </si>
+  <si>
+    <t>Us maybe visit.</t>
+  </si>
+  <si>
+    <t>Jonathan Clark</t>
+  </si>
+  <si>
+    <t>Around up page off president.</t>
+  </si>
+  <si>
+    <t>Alexander Gonzalez</t>
+  </si>
+  <si>
+    <t>1979</t>
+  </si>
+  <si>
+    <t>Involve last.</t>
+  </si>
+  <si>
+    <t>Mark Klein</t>
+  </si>
+  <si>
+    <t>Easy among fine.</t>
+  </si>
+  <si>
+    <t>Daniel Church</t>
+  </si>
+  <si>
+    <t>Street tough name.</t>
+  </si>
+  <si>
+    <t>Kelsey Robbins</t>
+  </si>
+  <si>
+    <t>Do land keep life.</t>
+  </si>
+  <si>
+    <t>Jesus Jones</t>
+  </si>
+  <si>
+    <t>Sometimes end product feel.</t>
+  </si>
+  <si>
+    <t>Melissa Wells</t>
+  </si>
+  <si>
+    <t>Medical never stay as.</t>
+  </si>
+  <si>
+    <t>Lauren Hall</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>Check summer.</t>
+  </si>
+  <si>
+    <t>Shirley Moran</t>
+  </si>
+  <si>
+    <t>Close base.</t>
+  </si>
+  <si>
+    <t>Dana Hayes</t>
+  </si>
+  <si>
+    <t>Other current stock election.</t>
+  </si>
+  <si>
+    <t>Jorge Evans</t>
+  </si>
+  <si>
+    <t>Moment forward control doctor.</t>
+  </si>
+  <si>
+    <t>George Russell</t>
+  </si>
+  <si>
+    <t>Race campaign those despite.</t>
+  </si>
+  <si>
+    <t>Kyle Keller</t>
+  </si>
+  <si>
+    <t>Enter which.</t>
+  </si>
+  <si>
+    <t>Steve Chung</t>
+  </si>
+  <si>
+    <t>Eat tax pressure fish possible.</t>
+  </si>
+  <si>
+    <t>Eric Gonzalez</t>
+  </si>
+  <si>
+    <t>Tell during hospital.</t>
+  </si>
+  <si>
+    <t>Richard Harrison</t>
+  </si>
+  <si>
+    <t>Rather born who.</t>
+  </si>
+  <si>
+    <t>Julia Gomez</t>
+  </si>
+  <si>
+    <t>Green him available.</t>
+  </si>
+  <si>
+    <t>Laura Ware</t>
+  </si>
+  <si>
+    <t>Something half south mission.</t>
+  </si>
+  <si>
+    <t>Elizabeth Lloyd</t>
+  </si>
+  <si>
+    <t>She politics.</t>
+  </si>
+  <si>
+    <t>April Gonzalez</t>
   </si>
   <si>
     <t>2018</t>
   </si>
   <si>
-    <t>Think but manage kitchen.</t>
-  </si>
-  <si>
-    <t>Amy Potter</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>Service another pressure long edge.</t>
-  </si>
-  <si>
-    <t>Jody Clark</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>Investment but second.</t>
-  </si>
-  <si>
-    <t>Yvonne Rodriguez</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>Again relationship another.</t>
-  </si>
-  <si>
-    <t>Heidi Hicks</t>
-  </si>
-  <si>
-    <t>1989</t>
-  </si>
-  <si>
-    <t>Son get usually size.</t>
-  </si>
-  <si>
-    <t>Lauren Clark</t>
-  </si>
-  <si>
-    <t>1987</t>
-  </si>
-  <si>
-    <t>Develop manage she quality.</t>
-  </si>
-  <si>
-    <t>Mathew Henderson</t>
-  </si>
-  <si>
-    <t>1972</t>
-  </si>
-  <si>
-    <t>Expect civil sometimes.</t>
-  </si>
-  <si>
-    <t>Melissa Clark</t>
-  </si>
-  <si>
-    <t>1974</t>
-  </si>
-  <si>
-    <t>Describe friend light certain.</t>
-  </si>
-  <si>
-    <t>Robert Marshall</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>Gas force leader word pattern.</t>
-  </si>
-  <si>
-    <t>James Nguyen</t>
-  </si>
-  <si>
-    <t>1988</t>
-  </si>
-  <si>
-    <t>Fire about line draw.</t>
-  </si>
-  <si>
-    <t>Pamela Brown</t>
-  </si>
-  <si>
-    <t>Pull parent service network.</t>
-  </si>
-  <si>
-    <t>Dominique Arellano</t>
-  </si>
-  <si>
-    <t>Particularly market order.</t>
-  </si>
-  <si>
-    <t>Stephanie Yoder</t>
-  </si>
-  <si>
-    <t>Small to agreement president edge.</t>
-  </si>
-  <si>
-    <t>Matthew Boyer</t>
-  </si>
-  <si>
-    <t>Analysis letter so well could.</t>
-  </si>
-  <si>
-    <t>Christine Martin</t>
-  </si>
-  <si>
-    <t>1981</t>
-  </si>
-  <si>
-    <t>Head us song glass.</t>
-  </si>
-  <si>
-    <t>Eric Knight</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>Dream three.</t>
-  </si>
-  <si>
-    <t>Laura Hartman</t>
-  </si>
-  <si>
-    <t>Hot language however blood player.</t>
-  </si>
-  <si>
-    <t>Stephanie Miller</t>
-  </si>
-  <si>
-    <t>1993</t>
-  </si>
-  <si>
-    <t>Audience there.</t>
-  </si>
-  <si>
-    <t>Amanda Williams</t>
-  </si>
-  <si>
-    <t>Move case.</t>
-  </si>
-  <si>
-    <t>Tammy Jordan</t>
-  </si>
-  <si>
-    <t>A full fine model more.</t>
-  </si>
-  <si>
-    <t>Sophia Horton</t>
-  </si>
-  <si>
-    <t>Control much run institution.</t>
-  </si>
-  <si>
-    <t>Sandra Douglas</t>
-  </si>
-  <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>Speech simply sort.</t>
-  </si>
-  <si>
-    <t>Paul Burnett</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>Whether politics training experience.</t>
-  </si>
-  <si>
-    <t>Jill Harvey</t>
-  </si>
-  <si>
-    <t>Cause power four.</t>
-  </si>
-  <si>
-    <t>Brittany Perez</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>Material finally into better.</t>
-  </si>
-  <si>
-    <t>Jessica Oliver</t>
-  </si>
-  <si>
-    <t>Air true out reflect.</t>
-  </si>
-  <si>
-    <t>Stacey Johnson</t>
-  </si>
-  <si>
-    <t>Although guess race page result.</t>
-  </si>
-  <si>
-    <t>Thomas Wright</t>
-  </si>
-  <si>
-    <t>1977</t>
-  </si>
-  <si>
-    <t>Nature back smile.</t>
-  </si>
-  <si>
-    <t>Allen Harris</t>
-  </si>
-  <si>
-    <t>1978</t>
-  </si>
-  <si>
-    <t>Collection how bag big.</t>
-  </si>
-  <si>
-    <t>Dale Blackburn</t>
-  </si>
-  <si>
-    <t>1985</t>
-  </si>
-  <si>
-    <t>Nor issue edge pattern.</t>
-  </si>
-  <si>
-    <t>Amy Fitzpatrick</t>
-  </si>
-  <si>
-    <t>1979</t>
-  </si>
-  <si>
-    <t>Wrong smile live interesting.</t>
-  </si>
-  <si>
-    <t>Gregory Mccormick</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>Too have pass through.</t>
-  </si>
-  <si>
-    <t>Melissa Kelley</t>
-  </si>
-  <si>
-    <t>Allow opportunity dinner.</t>
-  </si>
-  <si>
-    <t>Ruben Stewart</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>Fine cause daughter half region.</t>
-  </si>
-  <si>
-    <t>Ryan Flynn</t>
-  </si>
-  <si>
-    <t>Want throw should.</t>
-  </si>
-  <si>
-    <t>Career late term.</t>
-  </si>
-  <si>
-    <t>Stefanie Manning</t>
-  </si>
-  <si>
-    <t>1970</t>
-  </si>
-  <si>
-    <t>Minute training cover.</t>
-  </si>
-  <si>
-    <t>Johnny Brewer</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>Expect economic natural.</t>
-  </si>
-  <si>
-    <t>James Fletcher</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>Science my population.</t>
-  </si>
-  <si>
-    <t>Julie Williams</t>
-  </si>
-  <si>
-    <t>Office kind mission change interesting.</t>
-  </si>
-  <si>
-    <t>Shannon Harrell DVM</t>
-  </si>
-  <si>
-    <t>Simply health item former.</t>
-  </si>
-  <si>
-    <t>Brad Lin</t>
-  </si>
-  <si>
-    <t>Reveal whose leave.</t>
-  </si>
-  <si>
-    <t>Lauren Gregory</t>
-  </si>
-  <si>
-    <t>1996</t>
-  </si>
-  <si>
-    <t>This include price.</t>
-  </si>
-  <si>
-    <t>Andrew Brown</t>
+    <t>Heart occur.</t>
+  </si>
+  <si>
+    <t>Jill Smith</t>
+  </si>
+  <si>
+    <t>Sign usually relate.</t>
+  </si>
+  <si>
+    <t>Kelly Hall</t>
+  </si>
+  <si>
+    <t>Enjoy shake talk.</t>
+  </si>
+  <si>
+    <t>Shane Gardner</t>
+  </si>
+  <si>
+    <t>Go news economic attorney girl.</t>
+  </si>
+  <si>
+    <t>Julia Moore</t>
+  </si>
+  <si>
+    <t>Must court contain organization.</t>
+  </si>
+  <si>
+    <t>John Hogan</t>
   </si>
   <si>
     <t>1986</t>
   </si>
   <si>
-    <t>May nation large support ago.</t>
-  </si>
-  <si>
-    <t>Mark Perkins</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>Feel himself court every.</t>
-  </si>
-  <si>
-    <t>Tracy Murphy</t>
-  </si>
-  <si>
-    <t>1975</t>
-  </si>
-  <si>
-    <t>Thing television generation let.</t>
-  </si>
-  <si>
-    <t>Kristen Cameron</t>
-  </si>
-  <si>
-    <t>Actually process improve back.</t>
-  </si>
-  <si>
-    <t>Sarah Shea</t>
-  </si>
-  <si>
-    <t>1997</t>
-  </si>
-  <si>
-    <t>Many must cultural have.</t>
-  </si>
-  <si>
-    <t>James Frazier</t>
-  </si>
-  <si>
-    <t>1984</t>
-  </si>
-  <si>
-    <t>Use public.</t>
-  </si>
-  <si>
-    <t>Joanna Moreno</t>
-  </si>
-  <si>
-    <t>Soon though.</t>
-  </si>
-  <si>
-    <t>Todd Werner</t>
-  </si>
-  <si>
-    <t>Reveal executive worker police.</t>
-  </si>
-  <si>
-    <t>Jacqueline Huffman</t>
-  </si>
-  <si>
-    <t>Car particularly.</t>
-  </si>
-  <si>
-    <t>Kyle Leach</t>
-  </si>
-  <si>
-    <t>1982</t>
-  </si>
-  <si>
-    <t>Country sing.</t>
-  </si>
-  <si>
-    <t>William Ray</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>Week support.</t>
-  </si>
-  <si>
-    <t>Robin Green</t>
-  </si>
-  <si>
-    <t>Although black.</t>
-  </si>
-  <si>
-    <t>Patricia Gardner</t>
-  </si>
-  <si>
-    <t>1991</t>
-  </si>
-  <si>
-    <t>Computer rule big star.</t>
-  </si>
-  <si>
-    <t>Kelly Galloway</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>Group billion.</t>
-  </si>
-  <si>
-    <t>Jennifer Wright</t>
-  </si>
-  <si>
-    <t>Professor better development.</t>
-  </si>
-  <si>
-    <t>Ryan Woodward</t>
-  </si>
-  <si>
-    <t>1980</t>
-  </si>
-  <si>
-    <t>Include surface per.</t>
-  </si>
-  <si>
-    <t>Jonathan Harvey</t>
-  </si>
-  <si>
-    <t>Heart development.</t>
-  </si>
-  <si>
-    <t>Sarah Ford</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>Thousand serious experience take dark.</t>
-  </si>
-  <si>
-    <t>Christopher Howard</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>Statement according car.</t>
-  </si>
-  <si>
-    <t>Nicole Berry</t>
-  </si>
-  <si>
-    <t>Change modern.</t>
-  </si>
-  <si>
-    <t>Michael Boyer</t>
-  </si>
-  <si>
-    <t>Set entire institution drop.</t>
-  </si>
-  <si>
-    <t>Sabrina Bishop</t>
-  </si>
-  <si>
-    <t>Leave not.</t>
-  </si>
-  <si>
-    <t>Michael Thompson</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>Green road.</t>
-  </si>
-  <si>
-    <t>Chris Wilkerson</t>
-  </si>
-  <si>
-    <t>Service man admit.</t>
-  </si>
-  <si>
-    <t>Joel Barber</t>
-  </si>
-  <si>
-    <t>1973</t>
-  </si>
-  <si>
-    <t>Research finally fish paper.</t>
-  </si>
-  <si>
-    <t>April Alvarado</t>
-  </si>
-  <si>
-    <t>At food hold.</t>
-  </si>
-  <si>
-    <t>David Logan</t>
-  </si>
-  <si>
-    <t>Nothing reveal set evidence there.</t>
-  </si>
-  <si>
-    <t>Andrea Page</t>
-  </si>
-  <si>
-    <t>Sea somebody character join.</t>
-  </si>
-  <si>
-    <t>Miss Morgan Griffin</t>
-  </si>
-  <si>
-    <t>Hard sell mean.</t>
-  </si>
-  <si>
-    <t>Cole Cook</t>
-  </si>
-  <si>
-    <t>Agreement pull rock very development.</t>
-  </si>
-  <si>
-    <t>Matthew Jones</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>Evidence just author same.</t>
-  </si>
-  <si>
-    <t>Brian Silva</t>
-  </si>
-  <si>
-    <t>Talk once recognize.</t>
-  </si>
-  <si>
-    <t>Paula Maddox</t>
-  </si>
-  <si>
-    <t>But process cut suddenly factor.</t>
-  </si>
-  <si>
-    <t>John Hickman</t>
-  </si>
-  <si>
-    <t>Peace determine we.</t>
-  </si>
-  <si>
-    <t>Charlotte Costa</t>
-  </si>
-  <si>
-    <t>Effect local purpose every.</t>
-  </si>
-  <si>
-    <t>Tamara Richardson</t>
-  </si>
-  <si>
-    <t>There store.</t>
-  </si>
-  <si>
-    <t>Robin Young</t>
-  </si>
-  <si>
-    <t>Huge require.</t>
-  </si>
-  <si>
-    <t>Joshua Gibson</t>
-  </si>
-  <si>
-    <t>Expert report information even.</t>
-  </si>
-  <si>
-    <t>Say not too.</t>
-  </si>
-  <si>
-    <t>Maria Williams</t>
-  </si>
-  <si>
-    <t>Near guy condition.</t>
-  </si>
-  <si>
-    <t>Shannon Johnson</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>Yourself not place fine.</t>
-  </si>
-  <si>
-    <t>Charles Werner</t>
-  </si>
-  <si>
-    <t>1995</t>
-  </si>
-  <si>
-    <t>Owner audience spring president space.</t>
-  </si>
-  <si>
-    <t>Annette Leon</t>
-  </si>
-  <si>
-    <t>Quality structure seven.</t>
-  </si>
-  <si>
-    <t>Jordan Jenkins</t>
-  </si>
-  <si>
-    <t>Skill majority another.</t>
-  </si>
-  <si>
-    <t>Christopher Gordon</t>
-  </si>
-  <si>
-    <t>Choose subject.</t>
-  </si>
-  <si>
-    <t>Danielle Le</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>Question work night.</t>
-  </si>
-  <si>
-    <t>Sarah Carpenter</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>Plant director increase decide one.</t>
-  </si>
-  <si>
-    <t>John Bishop</t>
-  </si>
-  <si>
-    <t>Democratic produce together material.</t>
-  </si>
-  <si>
-    <t>Rachel Davis</t>
-  </si>
-  <si>
-    <t>Six who middle.</t>
-  </si>
-  <si>
-    <t>Joshua Reeves</t>
-  </si>
-  <si>
-    <t>Hair tax.</t>
-  </si>
-  <si>
-    <t>Traci Scott</t>
-  </si>
-  <si>
-    <t>Less respond write lose.</t>
-  </si>
-  <si>
-    <t>Jesse Delgado</t>
-  </si>
-  <si>
-    <t>Time if election.</t>
-  </si>
-  <si>
-    <t>Alicia Bennett</t>
-  </si>
-  <si>
-    <t>Seek wish project.</t>
-  </si>
-  <si>
-    <t>Elizabeth Ryan</t>
-  </si>
-  <si>
-    <t>Stand between.</t>
-  </si>
-  <si>
-    <t>Chad Hall</t>
-  </si>
-  <si>
-    <t>Protect democratic.</t>
-  </si>
-  <si>
-    <t>Ray Bryant DDS</t>
-  </si>
-  <si>
-    <t>1983</t>
-  </si>
-  <si>
-    <t>Strategy value believe.</t>
-  </si>
-  <si>
-    <t>Adam Gutierrez</t>
-  </si>
-  <si>
-    <t>Data who.</t>
-  </si>
-  <si>
-    <t>Michael Grant</t>
-  </si>
-  <si>
-    <t>Dark ever term.</t>
-  </si>
-  <si>
-    <t>Jennifer Sanchez</t>
-  </si>
-  <si>
-    <t>Travel ask view book.</t>
-  </si>
-  <si>
-    <t>Michael Greene</t>
-  </si>
-  <si>
-    <t>Identify former.</t>
-  </si>
-  <si>
-    <t>Anna Byrd</t>
-  </si>
-  <si>
-    <t>Model reach bill beautiful reality.</t>
-  </si>
-  <si>
-    <t>Dominique Moore</t>
-  </si>
-  <si>
-    <t>So guy their each.</t>
-  </si>
-  <si>
-    <t>Sarah Willis</t>
-  </si>
-  <si>
-    <t>Us maybe visit.</t>
-  </si>
-  <si>
-    <t>Jonathan Clark</t>
-  </si>
-  <si>
-    <t>Around up page off president.</t>
-  </si>
-  <si>
-    <t>Alexander Gonzalez</t>
-  </si>
-  <si>
-    <t>Involve last.</t>
-  </si>
-  <si>
-    <t>Mark Klein</t>
-  </si>
-  <si>
-    <t>1990</t>
-  </si>
-  <si>
-    <t>Easy among fine.</t>
-  </si>
-  <si>
-    <t>Daniel Church</t>
-  </si>
-  <si>
-    <t>Street tough name.</t>
-  </si>
-  <si>
-    <t>Kelsey Robbins</t>
-  </si>
-  <si>
-    <t>Do land keep life.</t>
-  </si>
-  <si>
-    <t>Jesus Jones</t>
-  </si>
-  <si>
-    <t>1999</t>
-  </si>
-  <si>
-    <t>Sometimes end product feel.</t>
-  </si>
-  <si>
-    <t>Melissa Wells</t>
-  </si>
-  <si>
-    <t>Medical never stay as.</t>
-  </si>
-  <si>
-    <t>Lauren Hall</t>
-  </si>
-  <si>
-    <t>Check summer.</t>
-  </si>
-  <si>
-    <t>Shirley Moran</t>
-  </si>
-  <si>
-    <t>Close base.</t>
-  </si>
-  <si>
-    <t>Dana Hayes</t>
-  </si>
-  <si>
-    <t>Other current stock election.</t>
-  </si>
-  <si>
-    <t>Jorge Evans</t>
-  </si>
-  <si>
-    <t>Moment forward control doctor.</t>
-  </si>
-  <si>
-    <t>George Russell</t>
-  </si>
-  <si>
-    <t>1994</t>
-  </si>
-  <si>
-    <t>Race campaign those despite.</t>
-  </si>
-  <si>
-    <t>Kyle Keller</t>
-  </si>
-  <si>
-    <t>Enter which.</t>
-  </si>
-  <si>
-    <t>Steve Chung</t>
-  </si>
-  <si>
-    <t>Eat tax pressure fish possible.</t>
-  </si>
-  <si>
-    <t>Eric Gonzalez</t>
-  </si>
-  <si>
-    <t>Tell during hospital.</t>
-  </si>
-  <si>
-    <t>Richard Harrison</t>
-  </si>
-  <si>
-    <t>Rather born who.</t>
-  </si>
-  <si>
-    <t>Julia Gomez</t>
-  </si>
-  <si>
-    <t>Green him available.</t>
-  </si>
-  <si>
-    <t>Laura Ware</t>
-  </si>
-  <si>
-    <t>Something half south mission.</t>
-  </si>
-  <si>
-    <t>Elizabeth Lloyd</t>
-  </si>
-  <si>
-    <t>She politics.</t>
-  </si>
-  <si>
-    <t>April Gonzalez</t>
-  </si>
-  <si>
-    <t>Heart occur.</t>
-  </si>
-  <si>
-    <t>Jill Smith</t>
-  </si>
-  <si>
-    <t>Sign usually relate.</t>
-  </si>
-  <si>
-    <t>Kelly Hall</t>
-  </si>
-  <si>
-    <t>Enjoy shake talk.</t>
-  </si>
-  <si>
-    <t>Shane Gardner</t>
-  </si>
-  <si>
-    <t>Go news economic attorney girl.</t>
-  </si>
-  <si>
-    <t>Julia Moore</t>
-  </si>
-  <si>
-    <t>Must court contain organization.</t>
-  </si>
-  <si>
-    <t>John Hogan</t>
-  </si>
-  <si>
     <t>Your a energy if.</t>
   </si>
   <si>
@@ -1069,16 +1072,89 @@
   </si>
   <si>
     <t>Spencer Thomas</t>
+  </si>
+  <si>
+    <t>Method final message.</t>
+  </si>
+  <si>
+    <t>William Robinson</t>
+  </si>
+  <si>
+    <t>Pay also environment billion.</t>
+  </si>
+  <si>
+    <t>Terry Smith</t>
+  </si>
+  <si>
+    <t>Dinner explain kind.</t>
+  </si>
+  <si>
+    <t>Keith Tran</t>
+  </si>
+  <si>
+    <t>Sense candidate air husband.</t>
+  </si>
+  <si>
+    <t>Jody Reese</t>
+  </si>
+  <si>
+    <t>Situation purpose quickly dream.</t>
+  </si>
+  <si>
+    <t>Kelly Garcia</t>
+  </si>
+  <si>
+    <t>Second together store report population.</t>
+  </si>
+  <si>
+    <t>Ryan Larson</t>
+  </si>
+  <si>
+    <t>Follow movement per.</t>
+  </si>
+  <si>
+    <t>Christy Jackson</t>
+  </si>
+  <si>
+    <t>Choice door.</t>
+  </si>
+  <si>
+    <t>Gabriela Mendoza</t>
+  </si>
+  <si>
+    <t>Share society attack.</t>
+  </si>
+  <si>
+    <t>Anne Jackson</t>
+  </si>
+  <si>
+    <t>Itself military include child.</t>
+  </si>
+  <si>
+    <t>Gordon Murray</t>
+  </si>
+  <si>
+    <t>Nearly economy answer.</t>
+  </si>
+  <si>
+    <t>Rodney Henderson</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1104,8 +1180,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1408,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D148"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.6328125" customWidth="1"/>
@@ -1419,7 +1496,7 @@
     <col min="6" max="6" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1432,187 +1509,197 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <f>COUNTA(A2:A159)</f>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
       <c r="D14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -1620,13 +1707,13 @@
         <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -1634,1242 +1721,1242 @@
         <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D16" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D20" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D25" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D27" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B29" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B30" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="D39" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D40" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="D41" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="D44" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="D45" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B46" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B47" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="D47" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="B48" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="D49" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="D50" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B51" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D51" t="s">
-        <v>136</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B52" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B53" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B54" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D55" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D56" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D57" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="D58" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B60" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B61" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C61" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D61" t="s">
-        <v>161</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B62" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>159</v>
       </c>
       <c r="D62" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
       <c r="D63" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B64" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C64" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C65" t="s">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="D65" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C66" t="s">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="D66" t="s">
-        <v>174</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B67" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C67" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D67" t="s">
-        <v>177</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B68" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C69" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B70" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C70" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="D70" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B71" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="D71" t="s">
-        <v>186</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B72" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="D72" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B73" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C73" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="D73" t="s">
-        <v>191</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B74" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D74" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B75" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C75" t="s">
-        <v>6</v>
+        <v>199</v>
       </c>
       <c r="D75" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B76" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C76" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B77" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C77" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="D77" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B78" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C78" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="D78" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B79" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="D79" t="s">
-        <v>204</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B81" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="D81" t="s">
-        <v>144</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B82" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="D82" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B83" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D83" t="s">
-        <v>144</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B84" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C84" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B85" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C85" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="D85" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B86" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C86" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="D86" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B87" t="s">
         <v>48</v>
       </c>
       <c r="C87" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B88" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C88" t="s">
-        <v>6</v>
+        <v>226</v>
       </c>
       <c r="D88" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B89" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C89" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="D89" t="s">
-        <v>224</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B90" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C90" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D90" t="s">
-        <v>227</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B91" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C91" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D91" t="s">
-        <v>224</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B92" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C92" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="D92" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B93" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D93" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B94" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C94" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D94" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B95" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="D95" t="s">
-        <v>239</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B96" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C96" t="s">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B97" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C97" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="D97" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B98" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C98" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>161</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B99" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C99" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
       <c r="D99" t="s">
-        <v>136</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B100" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C100" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="D100" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B101" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C101" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D101" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B102" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C102" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="D102" t="s">
-        <v>239</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B103" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C103" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B104" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C104" t="s">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="D104" t="s">
-        <v>258</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
@@ -2880,10 +2967,10 @@
         <v>260</v>
       </c>
       <c r="C105" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="D105" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
@@ -2894,10 +2981,10 @@
         <v>262</v>
       </c>
       <c r="C106" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="D106" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
@@ -2908,10 +2995,10 @@
         <v>264</v>
       </c>
       <c r="C107" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D107" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
@@ -2922,10 +3009,10 @@
         <v>266</v>
       </c>
       <c r="C108" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D108" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
@@ -2936,10 +3023,10 @@
         <v>268</v>
       </c>
       <c r="C109" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
@@ -2950,10 +3037,10 @@
         <v>270</v>
       </c>
       <c r="C110" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D110" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
@@ -2964,10 +3051,10 @@
         <v>272</v>
       </c>
       <c r="C111" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="D111" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
@@ -2978,10 +3065,10 @@
         <v>274</v>
       </c>
       <c r="C112" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="D112" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
@@ -2992,24 +3079,24 @@
         <v>276</v>
       </c>
       <c r="C113" t="s">
-        <v>6</v>
+        <v>277</v>
       </c>
       <c r="D113" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B114" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C114" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="D114" t="s">
-        <v>279</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
@@ -3020,10 +3107,10 @@
         <v>281</v>
       </c>
       <c r="C115" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D115" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
@@ -3034,10 +3121,10 @@
         <v>283</v>
       </c>
       <c r="C116" t="s">
-        <v>6</v>
+        <v>277</v>
       </c>
       <c r="D116" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
@@ -3048,38 +3135,38 @@
         <v>285</v>
       </c>
       <c r="C117" t="s">
-        <v>6</v>
+        <v>105</v>
       </c>
       <c r="D117" t="s">
-        <v>286</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
+        <v>286</v>
+      </c>
+      <c r="B118" t="s">
         <v>287</v>
       </c>
-      <c r="B118" t="s">
-        <v>288</v>
-      </c>
       <c r="C118" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="D118" t="s">
-        <v>174</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
+        <v>288</v>
+      </c>
+      <c r="B119" t="s">
         <v>289</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>290</v>
       </c>
-      <c r="C119" t="s">
-        <v>6</v>
-      </c>
       <c r="D119" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
@@ -3090,10 +3177,10 @@
         <v>292</v>
       </c>
       <c r="C120" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D120" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
@@ -3104,10 +3191,10 @@
         <v>294</v>
       </c>
       <c r="C121" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D121" t="s">
-        <v>127</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
@@ -3118,10 +3205,10 @@
         <v>296</v>
       </c>
       <c r="C122" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="D122" t="s">
-        <v>239</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
@@ -3132,122 +3219,122 @@
         <v>298</v>
       </c>
       <c r="C123" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="D123" t="s">
-        <v>299</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
+        <v>299</v>
+      </c>
+      <c r="B124" t="s">
         <v>300</v>
       </c>
-      <c r="B124" t="s">
-        <v>301</v>
-      </c>
       <c r="C124" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="D124" t="s">
-        <v>258</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
+        <v>301</v>
+      </c>
+      <c r="B125" t="s">
         <v>302</v>
       </c>
-      <c r="B125" t="s">
-        <v>303</v>
-      </c>
       <c r="C125" t="s">
-        <v>6</v>
+        <v>142</v>
       </c>
       <c r="D125" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
+        <v>303</v>
+      </c>
+      <c r="B126" t="s">
         <v>304</v>
       </c>
-      <c r="B126" t="s">
-        <v>305</v>
-      </c>
       <c r="C126" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D126" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
+        <v>305</v>
+      </c>
+      <c r="B127" t="s">
         <v>306</v>
       </c>
-      <c r="B127" t="s">
-        <v>307</v>
-      </c>
       <c r="C127" t="s">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="D127" t="s">
-        <v>191</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
+        <v>307</v>
+      </c>
+      <c r="B128" t="s">
         <v>308</v>
       </c>
-      <c r="B128" t="s">
-        <v>309</v>
-      </c>
       <c r="C128" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="D128" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
+        <v>309</v>
+      </c>
+      <c r="B129" t="s">
         <v>310</v>
       </c>
-      <c r="B129" t="s">
-        <v>311</v>
-      </c>
       <c r="C129" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="D129" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
+        <v>311</v>
+      </c>
+      <c r="B130" t="s">
         <v>312</v>
       </c>
-      <c r="B130" t="s">
-        <v>313</v>
-      </c>
       <c r="C130" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="D130" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
+        <v>313</v>
+      </c>
+      <c r="B131" t="s">
         <v>314</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>315</v>
       </c>
-      <c r="C131" t="s">
-        <v>6</v>
-      </c>
       <c r="D131" t="s">
-        <v>204</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
@@ -3258,10 +3345,10 @@
         <v>317</v>
       </c>
       <c r="C132" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D132" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
@@ -3272,10 +3359,10 @@
         <v>319</v>
       </c>
       <c r="C133" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D133" t="s">
-        <v>156</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
@@ -3286,10 +3373,10 @@
         <v>321</v>
       </c>
       <c r="C134" t="s">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="D134" t="s">
-        <v>130</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
@@ -3300,10 +3387,10 @@
         <v>323</v>
       </c>
       <c r="C135" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="D135" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
@@ -3314,181 +3401,336 @@
         <v>325</v>
       </c>
       <c r="C136" t="s">
-        <v>6</v>
+        <v>326</v>
       </c>
       <c r="D136" t="s">
-        <v>136</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B137" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C137" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
       <c r="D137" t="s">
-        <v>204</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B138" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C138" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D138" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B139" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C139" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="D139" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B140" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C140" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="D140" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B141" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C141" t="s">
-        <v>6</v>
+        <v>116</v>
       </c>
       <c r="D141" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B142" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C142" t="s">
-        <v>6</v>
+        <v>123</v>
       </c>
       <c r="D142" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B143" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C143" t="s">
-        <v>6</v>
+        <v>290</v>
       </c>
       <c r="D143" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B144" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C144" t="s">
-        <v>6</v>
+        <v>102</v>
       </c>
       <c r="D144" t="s">
-        <v>115</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B145" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C145" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="D145" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B146" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C146" t="s">
-        <v>6</v>
+        <v>134</v>
       </c>
       <c r="D146" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B147" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C147" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="D147" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B148" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C148" t="s">
-        <v>6</v>
+        <v>204</v>
       </c>
       <c r="D148" t="s">
-        <v>161</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>351</v>
+      </c>
+      <c r="B149" t="s">
+        <v>352</v>
+      </c>
+      <c r="C149" t="s">
+        <v>73</v>
+      </c>
+      <c r="D149" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>353</v>
+      </c>
+      <c r="B150" t="s">
+        <v>354</v>
+      </c>
+      <c r="C150" t="s">
+        <v>116</v>
+      </c>
+      <c r="D150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>355</v>
+      </c>
+      <c r="B151" t="s">
+        <v>356</v>
+      </c>
+      <c r="C151" t="s">
+        <v>32</v>
+      </c>
+      <c r="D151" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>357</v>
+      </c>
+      <c r="B152" t="s">
+        <v>358</v>
+      </c>
+      <c r="C152" t="s">
+        <v>58</v>
+      </c>
+      <c r="D152" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>359</v>
+      </c>
+      <c r="B153" t="s">
+        <v>360</v>
+      </c>
+      <c r="C153" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>361</v>
+      </c>
+      <c r="B154" t="s">
+        <v>362</v>
+      </c>
+      <c r="C154" t="s">
+        <v>14</v>
+      </c>
+      <c r="D154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>363</v>
+      </c>
+      <c r="B155" t="s">
+        <v>364</v>
+      </c>
+      <c r="C155" t="s">
+        <v>83</v>
+      </c>
+      <c r="D155" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>365</v>
+      </c>
+      <c r="B156" t="s">
+        <v>366</v>
+      </c>
+      <c r="C156" t="s">
+        <v>93</v>
+      </c>
+      <c r="D156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>367</v>
+      </c>
+      <c r="B157" t="s">
+        <v>368</v>
+      </c>
+      <c r="C157" t="s">
+        <v>123</v>
+      </c>
+      <c r="D157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>369</v>
+      </c>
+      <c r="B158" t="s">
+        <v>370</v>
+      </c>
+      <c r="C158" t="s">
+        <v>111</v>
+      </c>
+      <c r="D158" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>371</v>
+      </c>
+      <c r="B159" t="s">
+        <v>372</v>
+      </c>
+      <c r="C159" t="s">
+        <v>58</v>
+      </c>
+      <c r="D159" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/storage/Librarie_Saint_Laurent.xlsx
+++ b/storage/Librarie_Saint_Laurent.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Information_Librarie_SL" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="375">
   <si>
     <t>Book_name</t>
   </si>
@@ -1138,6 +1138,12 @@
   </si>
   <si>
     <t>Rodney Henderson</t>
+  </si>
+  <si>
+    <t>Real fight.</t>
+  </si>
+  <si>
+    <t>Daniel Douglas</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="44.6328125" customWidth="1"/>
@@ -1527,8 +1533,8 @@
         <v>8</v>
       </c>
       <c r="E2">
-        <f>COUNTA(A2:A159)</f>
-        <v>158</v>
+        <f>COUNTA(A2:A160)</f>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -3729,8 +3735,22 @@
         <v>8</v>
       </c>
     </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>373</v>
+      </c>
+      <c r="B160" t="s">
+        <v>374</v>
+      </c>
+      <c r="C160" t="s">
+        <v>67</v>
+      </c>
+      <c r="D160" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
 </worksheet>
 </file>